--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -688,7 +692,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +757,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +822,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1208,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1273,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1338,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1403,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1533,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1598,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1663,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1728,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1729,7 +1793,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1858,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1916,7 +1988,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1977,7 +2053,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1990,7 +2070,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3674-585-CM26</t>
+          <t>619284-146-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2015,43 +2095,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.980.000-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>17577.25</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>619284-146-CM26</t>
+          <t>1057448-421-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,17 +2160,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.980.000-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2099,20 +2183,24 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2751.09</v>
+        <v>8979.690000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057448-421-CM26</t>
+          <t>2906-131-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2137,43 +2225,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8979.690000000001</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2906-131-CM26</t>
+          <t>4401-826-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2198,27 +2290,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2228,13 +2320,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>26610.78</v>
+        <v>49930.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4401-826-CM26</t>
+          <t>3674-585-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2259,37 +2351,41 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>49930.02</v>
+        <v>17577.25</v>
       </c>
     </row>
     <row r="31">
@@ -2343,7 +2439,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2404,7 +2504,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2569,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2526,7 +2634,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2699,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2764,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2722,7 +2842,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4044-689-CM26</t>
+          <t>894778-42-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2742,48 +2862,52 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>58970.45</v>
+        <v>332367</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2348-421-CM26</t>
+          <t>765-205-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2803,22 +2927,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2842,13 +2966,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>152784.1</v>
+        <v>183483.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>4044-689-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2868,32 +2992,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2907,13 +3031,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>332367</v>
+        <v>58970.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>765-205-CM26</t>
+          <t>2348-421-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2933,22 +3057,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2972,7 +3096,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>183483.72</v>
+        <v>152784.1</v>
       </c>
     </row>
     <row r="42">
@@ -3026,7 +3150,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3034,6 +3162,71 @@
       </c>
       <c r="M42" s="2" t="n">
         <v>39342.59</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>598-250-SE26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.513.000-1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Seidor Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.986.170-4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>340177.13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1160,7 +1160,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3880-448-CM26</t>
+          <t>3696-241-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26610.78</v>
+        <v>8923.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3696-241-CM26</t>
+          <t>3880-448-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8923.6</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="14">
@@ -1680,7 +1680,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4728-326-CM26</t>
+          <t>3695-420-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,27 +1705,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.719.000-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7221.61</v>
+        <v>923.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3695-420-CM26</t>
+          <t>2305-63-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1770,27 +1770,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>923.13</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2305-63-CM26</t>
+          <t>4728-326-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>60.719.000-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5158.29</v>
+        <v>7221.61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2434-37-CM26</t>
+          <t>2981-1144-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>120303.05</v>
+        <v>5772.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>979-1248-CM26</t>
+          <t>2434-37-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>28709.51</v>
+        <v>120303.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2981-1144-CM26</t>
+          <t>979-1248-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5772.69</v>
+        <v>28709.51</v>
       </c>
     </row>
     <row r="26">
@@ -2586,7 +2586,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>188-596-CM26</t>
+          <t>2341-499-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2626,32 +2626,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2235.26</v>
+        <v>34986</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>907581-33-CM26</t>
+          <t>1385462-180-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2676,27 +2672,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2710,13 +2706,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>57477</v>
+        <v>6039.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1385462-180-CM26</t>
+          <t>188-596-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2741,12 +2737,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2756,12 +2752,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2775,13 +2771,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6039.25</v>
+        <v>2235.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2341-499-CM26</t>
+          <t>907581-33-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2806,43 +2802,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>34986</v>
+        <v>57477</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>4044-689-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2862,32 +2862,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>332367</v>
+        <v>58970.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>765-205-CM26</t>
+          <t>894778-42-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2927,32 +2927,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>183483.72</v>
+        <v>332367</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4044-689-CM26</t>
+          <t>765-205-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2997,27 +2997,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>58970.45</v>
+        <v>183483.72</v>
       </c>
     </row>
     <row r="41">
@@ -3102,7 +3102,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1020-317-CM26</t>
+          <t>894778-43-SE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3161,71 +3161,136 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>39342.59</v>
+        <v>30212.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>1020-317-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>39342.59</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>598-250-SE26</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>61.513.000-1</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Seidor Chile S.A.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
         <v>340177.13</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>188-596-CM26</t>
+          <t>907581-33-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2737,27 +2737,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2235.26</v>
+        <v>57477</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>907581-33-CM26</t>
+          <t>188-596-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2836,13 +2836,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>57477</v>
+        <v>2235.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4044-689-CM26</t>
+          <t>2348-421-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2867,27 +2867,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>58970.45</v>
+        <v>152784.1</v>
       </c>
     </row>
     <row r="39">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2348-421-CM26</t>
+          <t>4044-689-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>152784.1</v>
+        <v>58970.45</v>
       </c>
     </row>
     <row r="42">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1020-317-CM26</t>
+          <t>812261-1397-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3207,90 +3207,151 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>39342.59</v>
+        <v>223910.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>1020-317-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>39342.59</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>598-250-SE26</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>61.513.000-1</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Seidor Chile S.A.</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>340177.13</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2026.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
